--- a/eval/results/SuppFile2_Stats_generated.xlsx
+++ b/eval/results/SuppFile2_Stats_generated.xlsx
@@ -1577,10 +1577,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F10" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
@@ -1589,16 +1589,16 @@
         <v>24</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0.6667</v>
+        <v>0.6733</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.987</v>
+        <v>0.9872</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.608</v>
+        <v>0.616</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>0.7524999999999999</v>
+        <v>0.7586000000000001</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1630,13 +1630,13 @@
         <v>0.8288</v>
       </c>
       <c r="X10" t="n">
-        <v>0.163</v>
+        <v>0.203</v>
       </c>
       <c r="Y10" t="n">
         <v>8</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.367</v>
+        <v>0.364</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1644,13 +1644,13 @@
         </is>
       </c>
       <c r="AC10" t="n">
-        <v>0.229</v>
+        <v>0.227</v>
       </c>
       <c r="AD10" t="n">
         <v>5</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.858</v>
+        <v>0.854</v>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
@@ -1658,13 +1658,13 @@
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>0.043</v>
+        <v>0.0582</v>
       </c>
       <c r="AI10" t="n">
         <v>6</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.129</v>
+        <v>0.175</v>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
@@ -1695,10 +1695,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G11" t="n">
         <v>5</v>
@@ -1707,16 +1707,16 @@
         <v>64</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0.8532999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.9275</v>
+        <v>0.9286</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0.7901</v>
+        <v>0.8025</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>0.8532999999999999</v>
+        <v>0.8609</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1724,10 +1724,10 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q11" t="n">
         <v>5</v>
@@ -1736,25 +1736,25 @@
         <v>64</v>
       </c>
       <c r="S11" s="2" t="n">
-        <v>0.8733</v>
+        <v>0.88</v>
       </c>
       <c r="T11" s="2" t="n">
-        <v>0.9306</v>
+        <v>0.9315</v>
       </c>
       <c r="U11" s="2" t="n">
-        <v>0.8272</v>
+        <v>0.8395</v>
       </c>
       <c r="V11" s="2" t="n">
-        <v>0.8758</v>
+        <v>0.8831</v>
       </c>
       <c r="X11" t="n">
-        <v>0.737</v>
+        <v>0.732</v>
       </c>
       <c r="Y11" t="n">
         <v>11</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.879</v>
+        <v>0.854</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="AI11" t="n">
         <v>11</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.776</v>
+        <v>0.767</v>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G16" t="n">
         <v>27</v>
@@ -2287,16 +2287,16 @@
         <v>56</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0.6867</v>
+        <v>0.6933</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.6351</v>
+        <v>0.64</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0.7015</v>
+        <v>0.7164</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>0.6667</v>
+        <v>0.6761</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -2328,13 +2328,13 @@
         <v>0.8397</v>
       </c>
       <c r="X16" t="n">
-        <v>0.000507</v>
+        <v>0.000797</v>
       </c>
       <c r="Y16" s="3" t="n">
         <v>2</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>0.00152</v>
+        <v>0.00239</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -2342,13 +2342,13 @@
         </is>
       </c>
       <c r="AC16" t="n">
-        <v>0.00339</v>
+        <v>0.00361</v>
       </c>
       <c r="AD16" s="3" t="n">
         <v>2</v>
       </c>
       <c r="AE16" s="3" t="n">
-        <v>0.00763</v>
+        <v>0.00812</v>
       </c>
       <c r="AF16" s="3" t="inlineStr">
         <is>
@@ -2356,13 +2356,13 @@
         </is>
       </c>
       <c r="AH16" t="n">
-        <v>0.155</v>
+        <v>0.219</v>
       </c>
       <c r="AI16" t="n">
         <v>9</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.279</v>
+        <v>0.329</v>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         <v>1</v>
       </c>
       <c r="Y22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z22" t="n">
         <v>1</v>
@@ -3010,7 +3010,7 @@
         <v>1</v>
       </c>
       <c r="Y23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z23" t="n">
         <v>1</v>
@@ -3236,7 +3236,7 @@
         <v>0.732</v>
       </c>
       <c r="Y25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z25" t="n">
         <v>0.84</v>
@@ -3406,10 +3406,10 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F27" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G27" t="n">
         <v>1</v>
@@ -3418,16 +3418,16 @@
         <v>24</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>0.6667</v>
+        <v>0.6733</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.987</v>
+        <v>0.9872</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0.608</v>
+        <v>0.616</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>0.7524999999999999</v>
+        <v>0.7586000000000001</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -3459,13 +3459,13 @@
         <v>0.7981</v>
       </c>
       <c r="X27" t="n">
-        <v>0.454</v>
+        <v>0.531</v>
       </c>
       <c r="Y27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.534</v>
+        <v>0.597</v>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
@@ -3473,13 +3473,13 @@
         </is>
       </c>
       <c r="AC27" t="n">
-        <v>0.624</v>
+        <v>0.623</v>
       </c>
       <c r="AD27" t="n">
         <v>12</v>
       </c>
       <c r="AE27" t="n">
-        <v>0.858</v>
+        <v>0.854</v>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
@@ -3487,13 +3487,13 @@
         </is>
       </c>
       <c r="AH27" t="n">
-        <v>0.291</v>
+        <v>0.354</v>
       </c>
       <c r="AI27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0.423</v>
+        <v>0.398</v>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
@@ -3519,10 +3519,10 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F28" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G28" t="n">
         <v>5</v>
@@ -3531,16 +3531,16 @@
         <v>64</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>0.8532999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.9275</v>
+        <v>0.9286</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0.7901</v>
+        <v>0.8025</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>0.8532999999999999</v>
+        <v>0.8609</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -3572,13 +3572,13 @@
         <v>0.8649</v>
       </c>
       <c r="X28" t="n">
-        <v>0.868</v>
+        <v>1</v>
       </c>
       <c r="Y28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.879</v>
+        <v>1</v>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
@@ -3586,7 +3586,7 @@
         </is>
       </c>
       <c r="AC28" t="n">
-        <v>0.718</v>
+        <v>0.719</v>
       </c>
       <c r="AD28" t="n">
         <v>13</v>
@@ -3914,7 +3914,7 @@
         <v>0.501</v>
       </c>
       <c r="Y31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z31" t="n">
         <v>1</v>
@@ -4027,7 +4027,7 @@
         <v>1</v>
       </c>
       <c r="Y32" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z32" t="n">
         <v>1</v>
@@ -4084,10 +4084,10 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F33" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G33" t="n">
         <v>27</v>
@@ -4096,16 +4096,16 @@
         <v>56</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>0.6867</v>
+        <v>0.6933</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.6351</v>
+        <v>0.64</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0.7015</v>
+        <v>0.7164</v>
       </c>
       <c r="L33" s="2" t="n">
-        <v>0.6667</v>
+        <v>0.6761</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -4137,13 +4137,13 @@
         <v>0.656</v>
       </c>
       <c r="X33" t="n">
-        <v>0.706</v>
+        <v>0.801</v>
       </c>
       <c r="Y33" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.901</v>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
@@ -4151,10 +4151,10 @@
         </is>
       </c>
       <c r="AC33" t="n">
-        <v>0.458</v>
+        <v>0.461</v>
       </c>
       <c r="AD33" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE33" t="n">
         <v>0.523</v>
@@ -4165,13 +4165,13 @@
         </is>
       </c>
       <c r="AH33" t="n">
-        <v>0.363</v>
+        <v>0.272</v>
       </c>
       <c r="AI33" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.408</v>
+        <v>0.35</v>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>1</v>
       </c>
       <c r="Y34" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z34" t="n">
         <v>1</v>
@@ -4495,7 +4495,7 @@
         <v>0.523</v>
       </c>
       <c r="AD38" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE38" t="n">
         <v>0.588</v>
@@ -4961,7 +4961,7 @@
         <v>0.713</v>
       </c>
       <c r="AI42" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ42" t="n">
         <v>0.727</v>
@@ -5074,7 +5074,7 @@
         <v>0.845</v>
       </c>
       <c r="AI43" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AJ43" t="n">
         <v>0.845</v>
@@ -5159,7 +5159,7 @@
         <v>0.619</v>
       </c>
       <c r="Y44" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z44" t="n">
         <v>1</v>
@@ -5173,7 +5173,7 @@
         <v>0.524</v>
       </c>
       <c r="AD44" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AE44" t="n">
         <v>1</v>
@@ -5216,10 +5216,10 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F45" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G45" t="n">
         <v>3</v>
@@ -5228,16 +5228,16 @@
         <v>22</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>0.6667</v>
+        <v>0.68</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.963</v>
+        <v>0.9639</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0.624</v>
+        <v>0.64</v>
       </c>
       <c r="L45" s="2" t="n">
-        <v>0.7573</v>
+        <v>0.7692</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0.7885</v>
       </c>
       <c r="X45" t="n">
-        <v>0.534</v>
+        <v>0.707</v>
       </c>
       <c r="Y45" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z45" t="n">
-        <v>0.534</v>
+        <v>0.707</v>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
@@ -5283,13 +5283,13 @@
         </is>
       </c>
       <c r="AC45" t="n">
-        <v>0.364</v>
+        <v>0.62</v>
       </c>
       <c r="AD45" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AE45" t="n">
-        <v>0.858</v>
+        <v>0.854</v>
       </c>
       <c r="AF45" t="inlineStr">
         <is>
@@ -5297,13 +5297,13 @@
         </is>
       </c>
       <c r="AH45" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.895</v>
       </c>
       <c r="AI45" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.895</v>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
         <v>0.673</v>
       </c>
       <c r="Y47" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z47" t="n">
         <v>0.673</v>
@@ -5738,7 +5738,7 @@
         <v>0.613</v>
       </c>
       <c r="AD49" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE49" t="n">
         <v>1</v>
@@ -6770,7 +6770,7 @@
         <v>0.113</v>
       </c>
       <c r="AI59" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ59" t="n">
         <v>0.17</v>
@@ -7025,10 +7025,10 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F62" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G62" t="n">
         <v>3</v>
@@ -7037,16 +7037,16 @@
         <v>22</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>0.6667</v>
+        <v>0.68</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.963</v>
+        <v>0.9639</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0.624</v>
+        <v>0.64</v>
       </c>
       <c r="L62" s="2" t="n">
-        <v>0.7573</v>
+        <v>0.7692</v>
       </c>
       <c r="N62" t="inlineStr">
         <is>
@@ -7078,13 +7078,13 @@
         <v>0.8326</v>
       </c>
       <c r="X62" t="n">
-        <v>0.127</v>
+        <v>0.2</v>
       </c>
       <c r="Y62" t="n">
         <v>10</v>
       </c>
       <c r="Z62" t="n">
-        <v>0.367</v>
+        <v>0.364</v>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
@@ -7106,13 +7106,13 @@
         </is>
       </c>
       <c r="AH62" t="n">
-        <v>0.0776</v>
+        <v>0.133</v>
       </c>
       <c r="AI62" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AJ62" t="n">
-        <v>0.175</v>
+        <v>0.239</v>
       </c>
       <c r="AK62" t="inlineStr">
         <is>
@@ -7900,7 +7900,7 @@
         <v>0.0873</v>
       </c>
       <c r="AI69" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ69" t="n">
         <v>0.177</v>
@@ -8015,7 +8015,7 @@
         <v>0.325</v>
       </c>
       <c r="AI72" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AJ72" t="n">
         <v>0.325</v>
@@ -8552,7 +8552,7 @@
         <v>0.368</v>
       </c>
       <c r="Y77" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z77" t="n">
         <v>0.414</v>
@@ -8835,10 +8835,10 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F80" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G80" t="n">
         <v>2</v>
@@ -8847,16 +8847,16 @@
         <v>23</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>0.6</v>
+        <v>0.6133</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.971</v>
+        <v>0.9718</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0.536</v>
+        <v>0.552</v>
       </c>
       <c r="L80" s="2" t="n">
-        <v>0.6907</v>
+        <v>0.7040999999999999</v>
       </c>
       <c r="N80" t="inlineStr">
         <is>
@@ -8888,13 +8888,13 @@
         <v>0.6378</v>
       </c>
       <c r="X80" t="n">
-        <v>0.483</v>
+        <v>0.349</v>
       </c>
       <c r="Y80" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z80" t="n">
-        <v>0.534</v>
+        <v>0.449</v>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
@@ -8916,13 +8916,13 @@
         </is>
       </c>
       <c r="AH80" t="n">
-        <v>0.376</v>
+        <v>0.255</v>
       </c>
       <c r="AI80" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AJ80" t="n">
-        <v>0.423</v>
+        <v>0.328</v>
       </c>
       <c r="AK80" t="inlineStr">
         <is>
@@ -9484,7 +9484,7 @@
         <v>0.367</v>
       </c>
       <c r="AI85" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ85" t="n">
         <v>0.503</v>
@@ -9600,7 +9600,7 @@
         <v>8</v>
       </c>
       <c r="AJ86" t="n">
-        <v>0.317</v>
+        <v>0.329</v>
       </c>
       <c r="AK86" t="inlineStr">
         <is>
@@ -10050,7 +10050,7 @@
         <v>0.352</v>
       </c>
       <c r="AI91" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AJ91" t="n">
         <v>0.792</v>
@@ -10644,10 +10644,10 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F97" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G97" t="n">
         <v>2</v>
@@ -10656,16 +10656,16 @@
         <v>23</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>0.6</v>
+        <v>0.6133</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.971</v>
+        <v>0.9718</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>0.536</v>
+        <v>0.552</v>
       </c>
       <c r="L97" s="2" t="n">
-        <v>0.6907</v>
+        <v>0.7040999999999999</v>
       </c>
       <c r="N97" t="inlineStr">
         <is>
@@ -10697,27 +10697,27 @@
         <v>0.8609</v>
       </c>
       <c r="X97" t="n">
-        <v>0.000679</v>
-      </c>
-      <c r="Y97" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z97" s="3" t="n">
-        <v>0.00611</v>
-      </c>
-      <c r="AA97" s="3" t="inlineStr">
+        <v>0.00156</v>
+      </c>
+      <c r="Y97" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z97" s="4" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="AA97" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
       <c r="AC97" t="n">
-        <v>0.481</v>
+        <v>0.477</v>
       </c>
       <c r="AD97" t="n">
         <v>12</v>
       </c>
       <c r="AE97" t="n">
-        <v>0.858</v>
+        <v>0.854</v>
       </c>
       <c r="AF97" t="inlineStr">
         <is>
@@ -10725,13 +10725,13 @@
         </is>
       </c>
       <c r="AH97" t="n">
-        <v>2.84e-05</v>
+        <v>8.27e-05</v>
       </c>
       <c r="AI97" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AJ97" s="3" t="n">
-        <v>0.000256</v>
+        <v>0.000744</v>
       </c>
       <c r="AK97" s="3" t="inlineStr">
         <is>
@@ -10786,10 +10786,10 @@
         </is>
       </c>
       <c r="O98" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P98" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q98" t="n">
         <v>7</v>
@@ -10798,25 +10798,25 @@
         <v>62</v>
       </c>
       <c r="S98" s="2" t="n">
-        <v>0.8333</v>
+        <v>0.84</v>
       </c>
       <c r="T98" s="2" t="n">
-        <v>0.9</v>
+        <v>0.9014</v>
       </c>
       <c r="U98" s="2" t="n">
-        <v>0.7778</v>
+        <v>0.7901</v>
       </c>
       <c r="V98" s="2" t="n">
-        <v>0.8344</v>
+        <v>0.8421</v>
       </c>
       <c r="X98" t="n">
-        <v>0.879</v>
+        <v>0.759</v>
       </c>
       <c r="Y98" t="n">
         <v>12</v>
       </c>
       <c r="Z98" t="n">
-        <v>0.879</v>
+        <v>0.854</v>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
@@ -10824,7 +10824,7 @@
         </is>
       </c>
       <c r="AC98" t="n">
-        <v>0.34</v>
+        <v>0.343</v>
       </c>
       <c r="AD98" t="n">
         <v>10</v>
@@ -10838,13 +10838,13 @@
         </is>
       </c>
       <c r="AH98" t="n">
-        <v>0.37</v>
+        <v>0.278</v>
       </c>
       <c r="AI98" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AJ98" t="n">
-        <v>0.555</v>
+        <v>0.5</v>
       </c>
       <c r="AK98" t="inlineStr">
         <is>
@@ -11067,7 +11067,7 @@
         <v>3.96e-05</v>
       </c>
       <c r="AI100" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AJ100" s="3" t="n">
         <v>0.000356</v>
@@ -11293,7 +11293,7 @@
         <v>7.38e-05</v>
       </c>
       <c r="AI102" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ102" s="3" t="n">
         <v>0.000664</v>
@@ -11406,10 +11406,10 @@
         <v>0.33</v>
       </c>
       <c r="AI103" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ103" t="n">
-        <v>0.408</v>
+        <v>0.371</v>
       </c>
       <c r="AK103" t="inlineStr">
         <is>
@@ -12060,49 +12060,49 @@
         <v>9</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>0.6667</v>
+        <v>0.6733</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>0.6667</v>
+        <v>0.68</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>0.6</v>
+        <v>0.6133</v>
       </c>
       <c r="G11" t="n">
         <v>9</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.987</v>
+        <v>0.9872</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.963</v>
+        <v>0.9639</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>0.971</v>
+        <v>0.9718</v>
       </c>
       <c r="L11" t="n">
         <v>9</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.608</v>
+        <v>0.616</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.624</v>
+        <v>0.64</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.536</v>
+        <v>0.552</v>
       </c>
       <c r="Q11" t="n">
         <v>9</v>
       </c>
       <c r="R11" s="6" t="n">
-        <v>0.7524999999999999</v>
+        <v>0.7586000000000001</v>
       </c>
       <c r="S11" s="6" t="n">
-        <v>0.7573</v>
+        <v>0.7692</v>
       </c>
       <c r="T11" s="6" t="n">
-        <v>0.6907</v>
+        <v>0.7040999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -12110,7 +12110,7 @@
         <v>10</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>0.8532999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="D12" s="6" t="n">
         <v>0.7867</v>
@@ -12122,7 +12122,7 @@
         <v>10</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.9275</v>
+        <v>0.9286</v>
       </c>
       <c r="I12" s="6" t="n">
         <v>0.9804</v>
@@ -12134,7 +12134,7 @@
         <v>10</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>0.7901</v>
+        <v>0.8025</v>
       </c>
       <c r="N12" s="6" t="n">
         <v>0.6173</v>
@@ -12146,7 +12146,7 @@
         <v>10</v>
       </c>
       <c r="R12" s="6" t="n">
-        <v>0.8532999999999999</v>
+        <v>0.8609</v>
       </c>
       <c r="S12" s="6" t="n">
         <v>0.7576000000000001</v>
@@ -12360,7 +12360,7 @@
         <v>15</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>0.6867</v>
+        <v>0.6933</v>
       </c>
       <c r="D17" s="6" t="n">
         <v>0.5133</v>
@@ -12372,7 +12372,7 @@
         <v>15</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.6351</v>
+        <v>0.64</v>
       </c>
       <c r="I17" s="6" t="n">
         <v>0.475</v>
@@ -12384,7 +12384,7 @@
         <v>15</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.7015</v>
+        <v>0.7164</v>
       </c>
       <c r="N17" s="6" t="n">
         <v>0.8507</v>
@@ -12396,7 +12396,7 @@
         <v>15</v>
       </c>
       <c r="R17" s="6" t="n">
-        <v>0.6667</v>
+        <v>0.6761</v>
       </c>
       <c r="S17" s="6" t="n">
         <v>0.6096</v>
@@ -13001,7 +13001,7 @@
         <v>10</v>
       </c>
       <c r="C32" s="6" t="n">
-        <v>0.8733</v>
+        <v>0.88</v>
       </c>
       <c r="D32" s="6" t="n">
         <v>0.8532999999999999</v>
@@ -13013,7 +13013,7 @@
         <v>10</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>0.9306</v>
+        <v>0.9315</v>
       </c>
       <c r="I32" s="6" t="n">
         <v>0.9683</v>
@@ -13025,7 +13025,7 @@
         <v>10</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.8272</v>
+        <v>0.8395</v>
       </c>
       <c r="N32" s="6" t="n">
         <v>0.7531</v>
@@ -13037,7 +13037,7 @@
         <v>10</v>
       </c>
       <c r="R32" s="6" t="n">
-        <v>0.8758</v>
+        <v>0.8831</v>
       </c>
       <c r="S32" s="6" t="n">
         <v>0.8472</v>
@@ -13356,10 +13356,10 @@
         <v>0.001</v>
       </c>
       <c r="D39" t="n">
-        <v>0.0136</v>
+        <v>0.0151</v>
       </c>
       <c r="E39" t="n">
-        <v>0.661</v>
+        <v>0.705</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -13367,13 +13367,13 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>0.09039999999999999</v>
+        <v>0.0911</v>
       </c>
       <c r="I39" t="n">
-        <v>0.000892</v>
+        <v>0.000899</v>
       </c>
       <c r="J39" t="n">
-        <v>0.0242</v>
+        <v>0.0243</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -13381,13 +13381,13 @@
         </is>
       </c>
       <c r="M39" t="n">
-        <v>0.0102</v>
+        <v>0.011</v>
       </c>
       <c r="N39" t="n">
-        <v>0.115</v>
+        <v>0.107</v>
       </c>
       <c r="O39" t="n">
-        <v>0.000634</v>
+        <v>0.000566</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -13395,13 +13395,13 @@
         </is>
       </c>
       <c r="R39" t="n">
-        <v>0.00322</v>
+        <v>0.00336</v>
       </c>
       <c r="S39" t="n">
-        <v>0.0134</v>
+        <v>0.0154</v>
       </c>
       <c r="T39" t="n">
-        <v>0.08989999999999999</v>
+        <v>0.08359999999999999</v>
       </c>
     </row>
     <row r="40">
@@ -13417,7 +13417,7 @@
         <v>0.00188</v>
       </c>
       <c r="E40" t="n">
-        <v>0.753</v>
+        <v>0.801</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -13439,10 +13439,10 @@
         </is>
       </c>
       <c r="M40" t="n">
-        <v>0.011</v>
+        <v>0.0132</v>
       </c>
       <c r="N40" t="n">
-        <v>0.156</v>
+        <v>0.14</v>
       </c>
       <c r="O40" t="n">
         <v>0.00377</v>
@@ -14014,7 +14014,7 @@
         <v>0.8733</v>
       </c>
       <c r="E54" s="6" t="n">
-        <v>0.8333</v>
+        <v>0.84</v>
       </c>
       <c r="G54" t="n">
         <v>10</v>
@@ -14026,7 +14026,7 @@
         <v>0.9559</v>
       </c>
       <c r="J54" s="6" t="n">
-        <v>0.9</v>
+        <v>0.9014</v>
       </c>
       <c r="L54" t="n">
         <v>10</v>
@@ -14038,7 +14038,7 @@
         <v>0.8025</v>
       </c>
       <c r="O54" s="6" t="n">
-        <v>0.7778</v>
+        <v>0.7901</v>
       </c>
       <c r="Q54" t="n">
         <v>10</v>
@@ -14050,7 +14050,7 @@
         <v>0.8725000000000001</v>
       </c>
       <c r="T54" s="6" t="n">
-        <v>0.8344</v>
+        <v>0.8421</v>
       </c>
     </row>
     <row r="55">
@@ -14360,13 +14360,13 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>0.347</v>
+        <v>0.412</v>
       </c>
       <c r="D61" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0094</v>
       </c>
       <c r="E61" t="n">
-        <v>0.914</v>
+        <v>0.93</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -14374,13 +14374,13 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>0.0254</v>
+        <v>0.0242</v>
       </c>
       <c r="I61" t="n">
-        <v>0.164</v>
+        <v>0.165</v>
       </c>
       <c r="J61" t="n">
-        <v>5.79e-05</v>
+        <v>5.82e-05</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
@@ -14388,13 +14388,13 @@
         </is>
       </c>
       <c r="M61" t="n">
-        <v>0.24</v>
+        <v>0.273</v>
       </c>
       <c r="N61" t="n">
-        <v>0.0551</v>
+        <v>0.058</v>
       </c>
       <c r="O61" t="n">
-        <v>3.17e-05</v>
+        <v>2.77e-05</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -14402,13 +14402,13 @@
         </is>
       </c>
       <c r="R61" t="n">
-        <v>0.526</v>
+        <v>0.487</v>
       </c>
       <c r="S61" t="n">
-        <v>0.00761</v>
+        <v>0.008160000000000001</v>
       </c>
       <c r="T61" t="n">
-        <v>0.24</v>
+        <v>0.238</v>
       </c>
     </row>
     <row r="62">
@@ -14418,10 +14418,10 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>0.293</v>
+        <v>0.362</v>
       </c>
       <c r="D62" t="n">
-        <v>0.008869999999999999</v>
+        <v>0.008920000000000001</v>
       </c>
       <c r="E62" t="n">
         <v>0.82</v>
@@ -14446,7 +14446,7 @@
         </is>
       </c>
       <c r="M62" t="n">
-        <v>0.221</v>
+        <v>0.198</v>
       </c>
       <c r="N62" t="n">
         <v>0.0555</v>
@@ -15367,13 +15367,13 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>0.01</v>
+        <v>0.0112</v>
       </c>
       <c r="D83" t="n">
-        <v>0.161</v>
+        <v>0.176</v>
       </c>
       <c r="E83" t="n">
-        <v>0.00558</v>
+        <v>0.00515</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -15381,13 +15381,13 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="I83" t="n">
-        <v>0.00718</v>
+        <v>0.00721</v>
       </c>
       <c r="J83" t="n">
-        <v>0.0514</v>
+        <v>0.0513</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
@@ -15395,13 +15395,13 @@
         </is>
       </c>
       <c r="M83" t="n">
-        <v>0.109</v>
+        <v>0.124</v>
       </c>
       <c r="N83" t="n">
-        <v>0.0131</v>
+        <v>0.0124</v>
       </c>
       <c r="O83" t="n">
-        <v>0.0026</v>
+        <v>0.00237</v>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
@@ -15409,13 +15409,13 @@
         </is>
       </c>
       <c r="R83" t="n">
-        <v>0.193</v>
+        <v>0.211</v>
       </c>
       <c r="S83" t="n">
-        <v>0.118</v>
+        <v>0.112</v>
       </c>
       <c r="T83" t="n">
-        <v>0.00275</v>
+        <v>0.00256</v>
       </c>
     </row>
     <row r="84">
@@ -15425,7 +15425,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>0.0243</v>
+        <v>0.0259</v>
       </c>
       <c r="D84" t="n">
         <v>0.423</v>
@@ -15453,13 +15453,13 @@
         </is>
       </c>
       <c r="M84" t="n">
-        <v>0.09950000000000001</v>
+        <v>0.112</v>
       </c>
       <c r="N84" t="n">
         <v>0.00898</v>
       </c>
       <c r="O84" t="n">
-        <v>0.00641</v>
+        <v>0.00539</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -15467,10 +15467,10 @@
         </is>
       </c>
       <c r="R84" t="n">
-        <v>0.0577</v>
+        <v>0.0654</v>
       </c>
       <c r="S84" t="n">
-        <v>0.175</v>
+        <v>0.159</v>
       </c>
       <c r="T84" t="n">
         <v>0.00121</v>
@@ -15628,13 +15628,13 @@
         <v>0.05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.914</v>
+        <v>0.93</v>
       </c>
       <c r="H2" t="n">
         <v>9</v>
       </c>
       <c r="I2" t="n">
-        <v>0.914</v>
+        <v>0.93</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -15642,13 +15642,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>5.79e-05</v>
+        <v>5.82e-05</v>
       </c>
       <c r="M2" t="n">
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>0.00104</v>
+        <v>0.00105</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -15656,13 +15656,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>3.17e-05</v>
+        <v>2.77e-05</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>0.00104</v>
+        <v>0.0009970000000000001</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -15670,13 +15670,13 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>0.24</v>
+        <v>0.238</v>
       </c>
       <c r="W2" t="n">
         <v>8</v>
       </c>
       <c r="X2" t="n">
-        <v>0.279</v>
+        <v>0.286</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -15707,13 +15707,13 @@
         <v>0.05</v>
       </c>
       <c r="G3" t="n">
-        <v>0.661</v>
+        <v>0.705</v>
       </c>
       <c r="H3" t="n">
         <v>8</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7</v>
+        <v>0.746</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -15721,13 +15721,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.0242</v>
+        <v>0.0243</v>
       </c>
       <c r="M3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0481</v>
+        <v>0.046</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -15735,13 +15735,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>0.000634</v>
+        <v>0.000566</v>
       </c>
       <c r="R3" t="n">
         <v>2</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0072</v>
+        <v>0.00679</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -15749,13 +15749,13 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>0.08989999999999999</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="W3" t="n">
         <v>5</v>
       </c>
       <c r="X3" t="n">
-        <v>0.141</v>
+        <v>0.137</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -15786,13 +15786,13 @@
         <v>0.05</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0136</v>
+        <v>0.0151</v>
       </c>
       <c r="H4" t="n">
         <v>5</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0288</v>
+        <v>0.0326</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -15800,7 +15800,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.000892</v>
+        <v>0.000899</v>
       </c>
       <c r="M4" t="n">
         <v>2</v>
@@ -15814,13 +15814,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>0.115</v>
+        <v>0.107</v>
       </c>
       <c r="R4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S4" t="n">
-        <v>0.163</v>
+        <v>0.161</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -15828,13 +15828,13 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>0.0134</v>
+        <v>0.0154</v>
       </c>
       <c r="W4" t="n">
         <v>4</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0288</v>
+        <v>0.0326</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -15879,13 +15879,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.09039999999999999</v>
+        <v>0.0911</v>
       </c>
       <c r="M5" t="n">
         <v>7</v>
       </c>
       <c r="N5" t="n">
-        <v>0.141</v>
+        <v>0.143</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -15893,13 +15893,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>0.0102</v>
+        <v>0.011</v>
       </c>
       <c r="R5" t="n">
         <v>4</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0262</v>
+        <v>0.0288</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -15907,13 +15907,13 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>0.00322</v>
+        <v>0.00336</v>
       </c>
       <c r="W5" t="n">
         <v>2</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0145</v>
+        <v>0.0151</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -15944,13 +15944,13 @@
         <v>0.05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.00558</v>
+        <v>0.00515</v>
       </c>
       <c r="H6" t="n">
         <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0223</v>
+        <v>0.0206</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -15958,13 +15958,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.0514</v>
+        <v>0.0513</v>
       </c>
       <c r="M6" t="n">
         <v>6</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0925</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -15972,13 +15972,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>0.0026</v>
+        <v>0.00237</v>
       </c>
       <c r="R6" t="n">
         <v>3</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0141</v>
+        <v>0.0132</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -15986,13 +15986,13 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>0.00275</v>
+        <v>0.00256</v>
       </c>
       <c r="W6" t="n">
         <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0141</v>
+        <v>0.0132</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -16023,13 +16023,13 @@
         <v>0.05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.161</v>
+        <v>0.176</v>
       </c>
       <c r="H7" t="n">
         <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>0.211</v>
+        <v>0.226</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -16037,13 +16037,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.00718</v>
+        <v>0.00721</v>
       </c>
       <c r="M7" t="n">
         <v>3</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0249</v>
+        <v>0.026</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -16051,13 +16051,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>0.0131</v>
+        <v>0.0124</v>
       </c>
       <c r="R7" t="n">
         <v>5</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0288</v>
+        <v>0.0298</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -16065,13 +16065,13 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>0.118</v>
+        <v>0.112</v>
       </c>
       <c r="W7" t="n">
         <v>6</v>
       </c>
       <c r="X7" t="n">
-        <v>0.163</v>
+        <v>0.161</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -16102,13 +16102,13 @@
         <v>0.05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0094</v>
       </c>
       <c r="H8" t="n">
         <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0262</v>
+        <v>0.0282</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -16116,13 +16116,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.164</v>
+        <v>0.165</v>
       </c>
       <c r="M8" t="n">
         <v>8</v>
       </c>
       <c r="N8" t="n">
-        <v>0.211</v>
+        <v>0.22</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -16130,13 +16130,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>0.0551</v>
+        <v>0.058</v>
       </c>
       <c r="R8" t="n">
         <v>6</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0945</v>
+        <v>0.0994</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -16144,13 +16144,13 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>0.00761</v>
+        <v>0.008160000000000001</v>
       </c>
       <c r="W8" t="n">
         <v>3</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0249</v>
+        <v>0.0267</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -16181,13 +16181,13 @@
         <v>0.05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01</v>
+        <v>0.0112</v>
       </c>
       <c r="H9" t="n">
         <v>4</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0262</v>
+        <v>0.0288</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -16195,13 +16195,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="M9" t="n">
         <v>9</v>
       </c>
       <c r="N9" t="n">
-        <v>0.832</v>
+        <v>0.823</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -16209,13 +16209,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>0.109</v>
+        <v>0.124</v>
       </c>
       <c r="R9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S9" t="n">
-        <v>0.163</v>
+        <v>0.172</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -16223,13 +16223,13 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>0.193</v>
+        <v>0.211</v>
       </c>
       <c r="W9" t="n">
         <v>7</v>
       </c>
       <c r="X9" t="n">
-        <v>0.24</v>
+        <v>0.262</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -16260,13 +16260,13 @@
         <v>0.05</v>
       </c>
       <c r="G10" t="n">
-        <v>0.347</v>
+        <v>0.412</v>
       </c>
       <c r="H10" t="n">
         <v>7</v>
       </c>
       <c r="I10" t="n">
-        <v>0.39</v>
+        <v>0.463</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -16274,13 +16274,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.0254</v>
+        <v>0.0242</v>
       </c>
       <c r="M10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0481</v>
+        <v>0.046</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -16288,13 +16288,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>0.24</v>
+        <v>0.273</v>
       </c>
       <c r="R10" t="n">
         <v>9</v>
       </c>
       <c r="S10" t="n">
-        <v>0.279</v>
+        <v>0.317</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -16302,13 +16302,13 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>0.526</v>
+        <v>0.487</v>
       </c>
       <c r="W10" t="n">
         <v>9</v>
       </c>
       <c r="X10" t="n">
-        <v>0.574</v>
+        <v>0.531</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -16388,7 +16388,7 @@
         <v>8</v>
       </c>
       <c r="X12" t="n">
-        <v>0.265</v>
+        <v>0.262</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -16447,13 +16447,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>0.156</v>
+        <v>0.14</v>
       </c>
       <c r="R13" t="n">
         <v>8</v>
       </c>
       <c r="S13" t="n">
-        <v>0.216</v>
+        <v>0.194</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -16504,7 +16504,7 @@
         <v>4</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0233</v>
+        <v>0.0238</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -16526,13 +16526,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>0.00641</v>
+        <v>0.00539</v>
       </c>
       <c r="R14" t="n">
         <v>3</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0192</v>
+        <v>0.0176</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>0.011</v>
+        <v>0.0132</v>
       </c>
       <c r="R15" t="n">
         <v>5</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0233</v>
+        <v>0.028</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -16698,13 +16698,13 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>0.175</v>
+        <v>0.159</v>
       </c>
       <c r="W16" t="n">
         <v>7</v>
       </c>
       <c r="X16" t="n">
-        <v>0.233</v>
+        <v>0.212</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -16735,13 +16735,13 @@
         <v>0.05</v>
       </c>
       <c r="G17" t="n">
-        <v>0.293</v>
+        <v>0.362</v>
       </c>
       <c r="H17" t="n">
         <v>6</v>
       </c>
       <c r="I17" t="n">
-        <v>0.34</v>
+        <v>0.42</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -16763,13 +16763,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>0.221</v>
+        <v>0.198</v>
       </c>
       <c r="R17" t="n">
         <v>9</v>
       </c>
       <c r="S17" t="n">
-        <v>0.265</v>
+        <v>0.255</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -16814,13 +16814,13 @@
         <v>0.05</v>
       </c>
       <c r="G18" t="n">
-        <v>0.753</v>
+        <v>0.801</v>
       </c>
       <c r="H18" t="n">
         <v>8</v>
       </c>
       <c r="I18" t="n">
-        <v>0.797</v>
+        <v>0.843</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -16862,7 +16862,7 @@
         <v>6</v>
       </c>
       <c r="X18" t="n">
-        <v>0.151</v>
+        <v>0.158</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -16893,7 +16893,7 @@
         <v>0.05</v>
       </c>
       <c r="G19" t="n">
-        <v>0.008869999999999999</v>
+        <v>0.008920000000000001</v>
       </c>
       <c r="H19" t="n">
         <v>3</v>
@@ -16927,7 +16927,7 @@
         <v>6</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0944</v>
+        <v>0.0951</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -16941,7 +16941,7 @@
         <v>3</v>
       </c>
       <c r="X19" t="n">
-        <v>0.0192</v>
+        <v>0.0189</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -16972,17 +16972,17 @@
         <v>0.05</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0243</v>
+        <v>0.0259</v>
       </c>
       <c r="H20" t="n">
         <v>5</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0486</v>
+        <v>0.0518</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="L20" t="n">
@@ -17000,13 +17000,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>0.09950000000000001</v>
+        <v>0.112</v>
       </c>
       <c r="R20" t="n">
         <v>7</v>
       </c>
       <c r="S20" t="n">
-        <v>0.149</v>
+        <v>0.161</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -17014,13 +17014,13 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>0.0577</v>
+        <v>0.0654</v>
       </c>
       <c r="W20" t="n">
         <v>5</v>
       </c>
       <c r="X20" t="n">
-        <v>0.0944</v>
+        <v>0.107</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
